--- a/artfynd/A 32482-2019 artfynd.xlsx
+++ b/artfynd/A 32482-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125474531</v>
       </c>
       <c r="B2" t="n">
-        <v>91172</v>
+        <v>91326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32482-2019 artfynd.xlsx
+++ b/artfynd/A 32482-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125474531</v>
       </c>
       <c r="B2" t="n">
-        <v>91380</v>
+        <v>91387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32482-2019 artfynd.xlsx
+++ b/artfynd/A 32482-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125474531</v>
       </c>
       <c r="B2" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32482-2019 artfynd.xlsx
+++ b/artfynd/A 32482-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125474531</v>
       </c>
       <c r="B2" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32482-2019 artfynd.xlsx
+++ b/artfynd/A 32482-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125474531</v>
       </c>
       <c r="B2" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
